--- a/BY_Trans.xlsx
+++ b/BY_Trans.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\VerveStacks\assumptions\VerveStacks_ISO_template\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VerveStacks_NZL_EECA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69D1EB1B-B45C-4149-AEE2-7B3180C9E8C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{172D3DBF-5749-46BF-8660-FEC29FEA4703}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28702" yWindow="-98" windowWidth="28995" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="misc." sheetId="2" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="58">
   <si>
     <t>attribute</t>
   </si>
@@ -42,9 +42,6 @@
     <t>attrib_cond</t>
   </si>
   <si>
-    <t>ncap_pasti</t>
-  </si>
-  <si>
     <t>~TFM_INS-TS</t>
   </si>
   <si>
@@ -57,161 +54,167 @@
     <t>process</t>
   </si>
   <si>
+    <t>act_bnd</t>
+  </si>
+  <si>
+    <t>rcap_bnd</t>
+  </si>
+  <si>
+    <t>pset_ci</t>
+  </si>
+  <si>
+    <t>ep_*</t>
+  </si>
+  <si>
+    <t>coal,oil,gas</t>
+  </si>
+  <si>
+    <t>limtype</t>
+  </si>
+  <si>
+    <t>up</t>
+  </si>
+  <si>
+    <t>ele</t>
+  </si>
+  <si>
+    <t>*</t>
+  </si>
+  <si>
+    <t>~TFM_INS</t>
+  </si>
+  <si>
+    <t>other_indexes</t>
+  </si>
+  <si>
+    <t>timeslice</t>
+  </si>
+  <si>
+    <t>allregions</t>
+  </si>
+  <si>
+    <t>commodity</t>
+  </si>
+  <si>
+    <t>assuming 6h storage capacity for day-night operation of pumped hydro</t>
+  </si>
+  <si>
+    <t>NCAP_AFAC</t>
+  </si>
+  <si>
+    <t>ELC</t>
+  </si>
+  <si>
+    <t>NCAP_AFC</t>
+  </si>
+  <si>
+    <t>ACT</t>
+  </si>
+  <si>
+    <t>DAYNITE</t>
+  </si>
+  <si>
+    <t>NRG</t>
+  </si>
+  <si>
+    <t>takes 9h to full charge (pump has a smaller capacity than the hydro turbine)</t>
+  </si>
+  <si>
+    <t>STG_EFF</t>
+  </si>
+  <si>
+    <t>FLO_FUNC</t>
+  </si>
+  <si>
+    <t>AuxStoOUT</t>
+  </si>
+  <si>
+    <t>~TFM_TOPINS-A</t>
+  </si>
+  <si>
+    <t>value</t>
+  </si>
+  <si>
+    <t>OUT</t>
+  </si>
+  <si>
+    <t>ELE</t>
+  </si>
+  <si>
+    <t>-life</t>
+  </si>
+  <si>
+    <t>life</t>
+  </si>
+  <si>
+    <t>flo_emis</t>
+  </si>
+  <si>
+    <t>gas</t>
+  </si>
+  <si>
+    <t>co2captured</t>
+  </si>
+  <si>
+    <t>co2</t>
+  </si>
+  <si>
+    <t>*ccs,*ccs-rf</t>
+  </si>
+  <si>
+    <t>coal,oil</t>
+  </si>
+  <si>
+    <t>-hydro</t>
+  </si>
+  <si>
+    <t>hydro</t>
+  </si>
+  <si>
+    <t>start</t>
+  </si>
+  <si>
+    <t>ncap_iled</t>
+  </si>
+  <si>
+    <t>solar</t>
+  </si>
+  <si>
+    <t>windon</t>
+  </si>
+  <si>
+    <t>windoff</t>
+  </si>
+  <si>
+    <t>-ncap_pasti</t>
+  </si>
+  <si>
+    <t>-ncap_af</t>
+  </si>
+  <si>
+    <t>ncap_af</t>
+  </si>
+  <si>
+    <t>ep_m_*</t>
+  </si>
+  <si>
+    <t>*_hydro_ps*</t>
+  </si>
+  <si>
+    <t>-prc_capact</t>
+  </si>
+  <si>
     <t>ncap_bnd</t>
   </si>
   <si>
-    <t>act_bnd</t>
-  </si>
-  <si>
-    <t>rcap_bnd</t>
-  </si>
-  <si>
-    <t>pset_ci</t>
-  </si>
-  <si>
-    <t>ep_*</t>
-  </si>
-  <si>
-    <t>coal,oil,gas</t>
-  </si>
-  <si>
-    <t>limtype</t>
-  </si>
-  <si>
-    <t>up</t>
-  </si>
-  <si>
-    <t>ele</t>
-  </si>
-  <si>
-    <t>*</t>
-  </si>
-  <si>
-    <t>~TFM_INS</t>
-  </si>
-  <si>
-    <t>other_indexes</t>
-  </si>
-  <si>
-    <t>timeslice</t>
-  </si>
-  <si>
-    <t>allregions</t>
-  </si>
-  <si>
-    <t>commodity</t>
-  </si>
-  <si>
-    <t>assuming 6h storage capacity for day-night operation of pumped hydro</t>
-  </si>
-  <si>
-    <t>NCAP_AFAC</t>
-  </si>
-  <si>
-    <t>ELC</t>
-  </si>
-  <si>
-    <t>NCAP_AFC</t>
-  </si>
-  <si>
-    <t>ACT</t>
-  </si>
-  <si>
-    <t>DAYNITE</t>
-  </si>
-  <si>
-    <t>NRG</t>
-  </si>
-  <si>
-    <t>takes 9h to full charge (pump has a smaller capacity than the hydro turbine)</t>
-  </si>
-  <si>
-    <t>STG_EFF</t>
-  </si>
-  <si>
-    <t>FLO_FUNC</t>
-  </si>
-  <si>
-    <t>AuxStoOUT</t>
-  </si>
-  <si>
-    <t>~TFM_TOPINS-A</t>
-  </si>
-  <si>
-    <t>value</t>
-  </si>
-  <si>
-    <t>OUT</t>
-  </si>
-  <si>
-    <t>ELE</t>
-  </si>
-  <si>
-    <t>-life</t>
-  </si>
-  <si>
-    <t>life</t>
-  </si>
-  <si>
-    <t>flo_emis</t>
-  </si>
-  <si>
-    <t>gas</t>
-  </si>
-  <si>
-    <t>co2captured</t>
-  </si>
-  <si>
-    <t>co2</t>
-  </si>
-  <si>
-    <t>*ccs,*ccs-rf</t>
-  </si>
-  <si>
-    <t>coal,oil</t>
-  </si>
-  <si>
-    <t>-hydro</t>
-  </si>
-  <si>
-    <t>hydro</t>
-  </si>
-  <si>
-    <t>start</t>
-  </si>
-  <si>
-    <t>ncap_iled</t>
-  </si>
-  <si>
-    <t>solar</t>
-  </si>
-  <si>
-    <t>windon</t>
-  </si>
-  <si>
-    <t>windoff</t>
-  </si>
-  <si>
-    <t>-ncap_pasti</t>
-  </si>
-  <si>
-    <t>-ncap_af</t>
-  </si>
-  <si>
-    <t>ncap_af</t>
-  </si>
-  <si>
-    <t>ep_m_*</t>
-  </si>
-  <si>
-    <t>*_hydro_ps*</t>
+    <t>RESID</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -231,6 +234,14 @@
       <b/>
       <sz val="11"/>
       <color theme="3"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -276,11 +287,12 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="2"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Heading 2" xfId="1" builtinId="17"/>
@@ -631,7 +643,7 @@
   <sheetData>
     <row r="3" spans="2:12" ht="17.649999999999999" thickBot="1" x14ac:dyDescent="0.6">
       <c r="B3" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="2:12" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
@@ -639,13 +651,13 @@
         <v>0</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>6</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>1</v>
@@ -660,38 +672,41 @@
         <v>2030</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B5" t="s">
-        <v>7</v>
+      <c r="B5" s="4" t="s">
+        <v>56</v>
       </c>
       <c r="E5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F5" t="s">
-        <v>2</v>
+        <v>57</v>
       </c>
       <c r="G5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J5" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B6" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C6" t="s">
-        <v>15</v>
+        <v>13</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>55</v>
       </c>
       <c r="H6">
         <v>8.76</v>
@@ -699,10 +714,10 @@
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B7" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E7" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G7">
         <v>4</v>
@@ -711,18 +726,18 @@
         <v>0</v>
       </c>
       <c r="J7" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" t="s">
         <v>9</v>
-      </c>
-      <c r="D8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E8" t="s">
-        <v>11</v>
       </c>
       <c r="G8">
         <v>4</v>
@@ -731,21 +746,21 @@
         <v>0</v>
       </c>
       <c r="J8" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B9" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C9" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H9">
         <v>40</v>
@@ -753,16 +768,16 @@
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B10" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C10" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D10" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H10">
         <v>100</v>
@@ -770,16 +785,16 @@
     </row>
     <row r="11" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B11" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C11" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="H11">
         <v>0.9</v>
@@ -787,53 +802,53 @@
     </row>
     <row r="12" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B12" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D12" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E12" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="H12">
         <v>0.95</v>
       </c>
       <c r="K12" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="L12" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B13" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D13" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E13" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="H13">
         <v>0.85</v>
       </c>
       <c r="K13" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="L13" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B14" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C14" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="H14">
         <v>2025</v>
@@ -841,7 +856,7 @@
     </row>
     <row r="20" spans="2:5" ht="17.649999999999999" thickBot="1" x14ac:dyDescent="0.6">
       <c r="B20" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21" spans="2:5" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
@@ -849,10 +864,10 @@
         <v>0</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>1</v>
@@ -860,58 +875,58 @@
     </row>
     <row r="22" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B22" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C22">
         <v>4</v>
       </c>
       <c r="D22" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="23" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B23" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C23">
         <v>1.5</v>
       </c>
       <c r="D23" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="24" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B24" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C24">
         <v>3</v>
       </c>
       <c r="D24" t="s">
+        <v>48</v>
+      </c>
+      <c r="E24" s="3" t="s">
         <v>50</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="25" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B25" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C25">
         <v>1.5</v>
       </c>
       <c r="D25" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -935,7 +950,7 @@
   <sheetData>
     <row r="3" spans="2:9" ht="17.649999999999999" thickBot="1" x14ac:dyDescent="0.6">
       <c r="B3" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="2:9" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
@@ -943,145 +958,145 @@
         <v>0</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="F4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G4" s="1" t="s">
         <v>19</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E5">
         <v>0.25</v>
       </c>
       <c r="F5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="I5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" t="s">
         <v>25</v>
-      </c>
-      <c r="C6" t="s">
-        <v>26</v>
-      </c>
-      <c r="D6" t="s">
-        <v>27</v>
       </c>
       <c r="E6">
         <v>0.31</v>
       </c>
       <c r="F6" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D7" t="s">
         <v>25</v>
-      </c>
-      <c r="C7" t="s">
-        <v>24</v>
-      </c>
-      <c r="D7" t="s">
-        <v>27</v>
       </c>
       <c r="E7">
         <v>1</v>
       </c>
       <c r="F7" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B8" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" t="s">
         <v>25</v>
-      </c>
-      <c r="C8" t="s">
-        <v>28</v>
-      </c>
-      <c r="D8" t="s">
-        <v>27</v>
       </c>
       <c r="E8">
         <v>0.67</v>
       </c>
       <c r="F8" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B9" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E9">
         <v>0.8</v>
       </c>
       <c r="F9" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="I9" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B10" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E10">
         <v>1.25</v>
       </c>
       <c r="F10" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G10" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13" spans="2:9" ht="17.649999999999999" thickBot="1" x14ac:dyDescent="0.6">
       <c r="B13" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14" spans="2:9" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B14" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="15" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B15" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C15" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D15" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>

--- a/BY_Trans.xlsx
+++ b/BY_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VerveStacks_NZL_EECA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{172D3DBF-5749-46BF-8660-FEC29FEA4703}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{849D3DE7-AB96-49FD-B2B3-03453D4A6B9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28702" yWindow="-98" windowWidth="28995" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="60">
   <si>
     <t>attribute</t>
   </si>
@@ -208,6 +208,12 @@
   </si>
   <si>
     <t>RESID</t>
+  </si>
+  <si>
+    <t>PASTI</t>
+  </si>
+  <si>
+    <t>ep*</t>
   </si>
 </sst>
 </file>
@@ -629,7 +635,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{982CB9B3-DA63-443B-9AA5-BEE16CBC2D59}">
-  <dimension ref="B3:L25"/>
+  <dimension ref="B3:L26"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="9.53125" bestFit="1" customWidth="1"/>
@@ -699,45 +705,45 @@
       </c>
     </row>
     <row r="6" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B6" t="s">
-        <v>3</v>
+      <c r="B6" s="4" t="s">
+        <v>56</v>
       </c>
       <c r="C6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="H6">
-        <v>8.76</v>
+        <v>34</v>
+      </c>
+      <c r="E6" t="s">
+        <v>59</v>
+      </c>
+      <c r="F6" t="s">
+        <v>58</v>
+      </c>
+      <c r="G6">
+        <v>2</v>
+      </c>
+      <c r="J6" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B7" t="s">
-        <v>6</v>
-      </c>
-      <c r="E7" t="s">
-        <v>53</v>
-      </c>
-      <c r="G7">
-        <v>4</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7" t="s">
-        <v>12</v>
+        <v>3</v>
+      </c>
+      <c r="C7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="H7">
+        <v>8.76</v>
       </c>
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D8" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E8" t="s">
-        <v>9</v>
+        <v>53</v>
       </c>
       <c r="G8">
         <v>4</v>
@@ -751,19 +757,22 @@
     </row>
     <row r="9" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B9" t="s">
-        <v>36</v>
-      </c>
-      <c r="C9" t="s">
-        <v>34</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="H9">
-        <v>40</v>
+        <v>7</v>
+      </c>
+      <c r="D9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E9" t="s">
+        <v>9</v>
+      </c>
+      <c r="G9">
+        <v>4</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.45">
@@ -773,51 +782,48 @@
       <c r="C10" t="s">
         <v>34</v>
       </c>
-      <c r="D10" t="s">
-        <v>44</v>
+      <c r="D10" s="3" t="s">
+        <v>43</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>35</v>
       </c>
       <c r="H10">
-        <v>100</v>
+        <v>40</v>
       </c>
     </row>
     <row r="11" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B11" s="3" t="s">
-        <v>52</v>
+      <c r="B11" t="s">
+        <v>36</v>
       </c>
       <c r="C11" t="s">
         <v>34</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="D11" t="s">
+        <v>44</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H11">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B12" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C12" t="s">
+        <v>34</v>
+      </c>
+      <c r="D12" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="F11" s="3" t="s">
+      <c r="F12" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="H11">
+      <c r="H12">
         <v>0.9</v>
-      </c>
-    </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B12" t="s">
-        <v>37</v>
-      </c>
-      <c r="D12" t="s">
-        <v>38</v>
-      </c>
-      <c r="E12" t="s">
-        <v>41</v>
-      </c>
-      <c r="H12">
-        <v>0.95</v>
-      </c>
-      <c r="K12" t="s">
-        <v>40</v>
-      </c>
-      <c r="L12" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.45">
@@ -825,13 +831,13 @@
         <v>37</v>
       </c>
       <c r="D13" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="E13" t="s">
         <v>41</v>
       </c>
       <c r="H13">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
       <c r="K13" t="s">
         <v>40</v>
@@ -842,49 +848,55 @@
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B14" t="s">
+        <v>37</v>
+      </c>
+      <c r="D14" t="s">
+        <v>42</v>
+      </c>
+      <c r="E14" t="s">
+        <v>41</v>
+      </c>
+      <c r="H14">
+        <v>0.85</v>
+      </c>
+      <c r="K14" t="s">
+        <v>40</v>
+      </c>
+      <c r="L14" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="15" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B15" t="s">
         <v>45</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C15" t="s">
         <v>34</v>
       </c>
-      <c r="F14" s="3" t="s">
+      <c r="F15" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="H14">
+      <c r="H15">
         <v>2025</v>
       </c>
     </row>
-    <row r="20" spans="2:5" ht="17.649999999999999" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B20" s="2" t="s">
+    <row r="21" spans="2:5" ht="17.649999999999999" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B21" s="2" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="21" spans="2:5" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B21" s="1" t="s">
+    <row r="22" spans="2:5" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B22" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="C22" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D21" s="1" t="s">
+      <c r="D22" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E21" s="1" t="s">
+      <c r="E22" s="1" t="s">
         <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B22" t="s">
-        <v>46</v>
-      </c>
-      <c r="C22">
-        <v>4</v>
-      </c>
-      <c r="D22" t="s">
-        <v>44</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="23" spans="2:5" x14ac:dyDescent="0.45">
@@ -892,10 +904,10 @@
         <v>46</v>
       </c>
       <c r="C23">
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="D23" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>50</v>
@@ -906,10 +918,10 @@
         <v>46</v>
       </c>
       <c r="C24">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="D24" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>50</v>
@@ -920,12 +932,26 @@
         <v>46</v>
       </c>
       <c r="C25">
+        <v>3</v>
+      </c>
+      <c r="D25" t="s">
+        <v>48</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="26" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B26" t="s">
+        <v>46</v>
+      </c>
+      <c r="C26">
         <v>1.5</v>
       </c>
-      <c r="D25" t="s">
+      <c r="D26" t="s">
         <v>49</v>
       </c>
-      <c r="E25" s="3" t="s">
+      <c r="E26" s="3" t="s">
         <v>50</v>
       </c>
     </row>
